--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-patient.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4954,7 +4954,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>174</v>
       </c>
@@ -4969,13 +4969,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5057,7 +5057,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>178</v>
       </c>
@@ -5072,13 +5072,13 @@
         <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
